--- a/data_raw/re_A030B_商品房平均销售价格_元_平方米.xlsx
+++ b/data_raw/re_A030B_商品房平均销售价格_元_平方米.xlsx
@@ -1,216 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2013</t>
-  </si>
-  <si>
-    <t>2014</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>2016</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>2018</t>
-  </si>
-  <si>
-    <t>2019</t>
-  </si>
-  <si>
-    <t>2020</t>
-  </si>
-  <si>
-    <t>2021</t>
-  </si>
-  <si>
-    <t>2022</t>
-  </si>
-  <si>
-    <t>2023</t>
-  </si>
-  <si>
-    <t>2024</t>
-  </si>
-  <si>
-    <t>2025</t>
-  </si>
-  <si>
-    <t>商品房平均销售价格(元/平方米)</t>
-  </si>
-  <si>
-    <t>上海</t>
-  </si>
-  <si>
-    <t>乌鲁木齐</t>
-  </si>
-  <si>
-    <t>兰州</t>
-  </si>
-  <si>
-    <t>北京</t>
-  </si>
-  <si>
-    <t>南京</t>
-  </si>
-  <si>
-    <t>南宁</t>
-  </si>
-  <si>
-    <t>南昌</t>
-  </si>
-  <si>
-    <t>厦门</t>
-  </si>
-  <si>
-    <t>合肥</t>
-  </si>
-  <si>
-    <t>呼和浩特</t>
-  </si>
-  <si>
-    <t>哈尔滨</t>
-  </si>
-  <si>
-    <t>大连</t>
-  </si>
-  <si>
-    <t>天津</t>
-  </si>
-  <si>
-    <t>太原</t>
-  </si>
-  <si>
-    <t>宁波</t>
-  </si>
-  <si>
-    <t>广州</t>
-  </si>
-  <si>
-    <t>成都</t>
-  </si>
-  <si>
-    <t>拉萨</t>
-  </si>
-  <si>
-    <t>昆明</t>
-  </si>
-  <si>
-    <t>杭州</t>
-  </si>
-  <si>
-    <t>武汉</t>
-  </si>
-  <si>
-    <t>沈阳</t>
-  </si>
-  <si>
-    <t>济南</t>
-  </si>
-  <si>
-    <t>海口</t>
-  </si>
-  <si>
-    <t>深圳</t>
-  </si>
-  <si>
-    <t>石家庄</t>
-  </si>
-  <si>
-    <t>福州</t>
-  </si>
-  <si>
-    <t>西宁</t>
-  </si>
-  <si>
-    <t>西安</t>
-  </si>
-  <si>
-    <t>贵阳</t>
-  </si>
-  <si>
-    <t>郑州</t>
-  </si>
-  <si>
-    <t>重庆</t>
-  </si>
-  <si>
-    <t>银川</t>
-  </si>
-  <si>
-    <t>长春</t>
-  </si>
-  <si>
-    <t>长沙</t>
-  </si>
-  <si>
-    <t>青岛</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -225,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -541,2251 +420,2424 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:U37"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21">
-      <c r="A1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:21">
-      <c r="A2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>商品房平均销售价格(元/平方米)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>上海</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>7196.00014583194</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>8360.99995512804</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>8195</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>12840</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>14464</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>14603.2352728002</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>14061.3739880608</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>16420</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>16787</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>20949</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>24747</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>23804</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>26890.0770227673</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>30677</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>33798</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>36102</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>40302</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>40170</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>41484</v>
       </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3">
+      <c r="U2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>乌鲁木齐</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>2166.36304445203</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="n">
         <v>2667.13602728414</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>3244</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="n">
         <v>3446</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="n">
         <v>4524</v>
       </c>
-      <c r="G3">
+      <c r="G3" t="n">
         <v>5253.78281215351</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="n">
         <v>5639.11745132869</v>
       </c>
-      <c r="I3">
+      <c r="I3" t="n">
         <v>6111</v>
       </c>
-      <c r="J3">
+      <c r="J3" t="n">
         <v>6429</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="n">
         <v>6669</v>
       </c>
-      <c r="L3">
+      <c r="L3" t="n">
         <v>6314</v>
       </c>
-      <c r="M3">
+      <c r="M3" t="n">
         <v>6668</v>
       </c>
-      <c r="N3">
+      <c r="N3" t="n">
         <v>8357.45620628848</v>
       </c>
-      <c r="O3">
+      <c r="O3" t="n">
         <v>8690</v>
       </c>
-      <c r="P3">
+      <c r="P3" t="n">
         <v>8081</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" t="n">
         <v>8116</v>
       </c>
-      <c r="R3">
+      <c r="R3" t="n">
         <v>8268</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="n">
         <v>8959</v>
       </c>
-      <c r="T3">
+      <c r="T3" t="n">
         <v>9442</v>
       </c>
-    </row>
-    <row r="4" spans="1:21">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4">
+      <c r="U3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>兰州</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>2614.24187129525</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="n">
         <v>2966.60204064562</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="n">
         <v>3145</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="n">
         <v>3624</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="n">
         <v>4233</v>
       </c>
-      <c r="G4">
+      <c r="G4" t="n">
         <v>4747.41248840502</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="n">
         <v>5697.51962435553</v>
       </c>
-      <c r="I4">
+      <c r="I4" t="n">
         <v>5868</v>
       </c>
-      <c r="J4">
+      <c r="J4" t="n">
         <v>6460</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="n">
         <v>6495</v>
       </c>
-      <c r="L4">
+      <c r="L4" t="n">
         <v>6601</v>
       </c>
-      <c r="M4">
+      <c r="M4" t="n">
         <v>7634</v>
       </c>
-      <c r="N4">
+      <c r="N4" t="n">
         <v>7923.93123890331</v>
       </c>
-      <c r="O4">
+      <c r="O4" t="n">
         <v>7626</v>
       </c>
-      <c r="P4">
+      <c r="P4" t="n">
         <v>8401</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" t="n">
         <v>7941</v>
       </c>
-      <c r="R4">
+      <c r="R4" t="n">
         <v>7977</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="n">
         <v>8656</v>
       </c>
-      <c r="T4">
+      <c r="T4" t="n">
         <v>8255</v>
       </c>
-    </row>
-    <row r="5" spans="1:21">
-      <c r="A5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5">
+      <c r="U4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>北京</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>8279.510133732019</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="n">
         <v>11553.2584783407</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="n">
         <v>12418</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="n">
         <v>13799</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="n">
         <v>17782</v>
       </c>
-      <c r="G5">
+      <c r="G5" t="n">
         <v>16851.9529366903</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="n">
         <v>17021.6326110424</v>
       </c>
-      <c r="I5">
+      <c r="I5" t="n">
         <v>18553</v>
       </c>
-      <c r="J5">
+      <c r="J5" t="n">
         <v>18833</v>
       </c>
-      <c r="K5">
+      <c r="K5" t="n">
         <v>22633</v>
       </c>
-      <c r="L5">
+      <c r="L5" t="n">
         <v>27497</v>
       </c>
-      <c r="M5">
+      <c r="M5" t="n">
         <v>32140</v>
       </c>
-      <c r="N5">
+      <c r="N5" t="n">
         <v>34142.8933603662</v>
       </c>
-      <c r="O5">
+      <c r="O5" t="n">
         <v>35905</v>
       </c>
-      <c r="P5">
+      <c r="P5" t="n">
         <v>37665</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" t="n">
         <v>40526</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="n">
         <v>38240</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="n">
         <v>37595</v>
       </c>
-      <c r="T5">
+      <c r="T5" t="n">
         <v>31976</v>
       </c>
-    </row>
-    <row r="6" spans="1:21">
-      <c r="A6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6">
+      <c r="U5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>南京</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>4477.0998568438</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="n">
         <v>5303.84249994947</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>5109</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>7185</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="n">
         <v>9565</v>
       </c>
-      <c r="G6">
+      <c r="G6" t="n">
         <v>9310.72428254883</v>
       </c>
-      <c r="H6">
+      <c r="H6" t="n">
         <v>10106.3556240545</v>
       </c>
-      <c r="I6">
+      <c r="I6" t="n">
         <v>11495</v>
       </c>
-      <c r="J6">
+      <c r="J6" t="n">
         <v>11198</v>
       </c>
-      <c r="K6">
+      <c r="K6" t="n">
         <v>11489</v>
       </c>
-      <c r="L6">
+      <c r="L6" t="n">
         <v>17754</v>
       </c>
-      <c r="M6">
+      <c r="M6" t="n">
         <v>15653</v>
       </c>
-      <c r="N6">
+      <c r="N6" t="n">
         <v>22379.8749635669</v>
       </c>
-      <c r="O6">
+      <c r="O6" t="n">
         <v>19007</v>
       </c>
-      <c r="P6">
+      <c r="P6" t="n">
         <v>24682</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" t="n">
         <v>26896</v>
       </c>
-      <c r="R6">
+      <c r="R6" t="n">
         <v>25768</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="n">
         <v>22599</v>
       </c>
-      <c r="T6">
+      <c r="T6" t="n">
         <v>17631</v>
       </c>
-    </row>
-    <row r="7" spans="1:21">
-      <c r="A7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7">
+      <c r="U6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>南宁</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>2872.42434124034</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="n">
         <v>3403.99986769306</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>3952</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>4557</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="n">
         <v>5135</v>
       </c>
-      <c r="G7">
+      <c r="G7" t="n">
         <v>5195.99713261971</v>
       </c>
-      <c r="H7">
+      <c r="H7" t="n">
         <v>6002.89310073851</v>
       </c>
-      <c r="I7">
+      <c r="I7" t="n">
         <v>6959</v>
       </c>
-      <c r="J7">
+      <c r="J7" t="n">
         <v>6627</v>
       </c>
-      <c r="K7">
+      <c r="K7" t="n">
         <v>6646</v>
       </c>
-      <c r="L7">
+      <c r="L7" t="n">
         <v>6887</v>
       </c>
-      <c r="M7">
+      <c r="M7" t="n">
         <v>7776</v>
       </c>
-      <c r="N7">
+      <c r="N7" t="n">
         <v>7782.17067460406</v>
       </c>
-      <c r="O7">
+      <c r="O7" t="n">
         <v>8406</v>
       </c>
-      <c r="P7">
+      <c r="P7" t="n">
         <v>8605</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" t="n">
         <v>8301</v>
       </c>
-      <c r="R7">
+      <c r="R7" t="n">
         <v>6680</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="n">
         <v>7602</v>
       </c>
-      <c r="T7">
+      <c r="T7" t="n">
         <v>6947</v>
       </c>
-    </row>
-    <row r="8" spans="1:21">
-      <c r="A8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8">
+      <c r="U7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>南昌</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>3125.97553019561</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>3558.05259865902</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>3461</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>3774</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="n">
         <v>4566</v>
       </c>
-      <c r="G8">
+      <c r="G8" t="n">
         <v>5939.30136708561</v>
       </c>
-      <c r="H8">
+      <c r="H8" t="n">
         <v>6418.97740152551</v>
       </c>
-      <c r="I8">
+      <c r="I8" t="n">
         <v>7101</v>
       </c>
-      <c r="J8">
+      <c r="J8" t="n">
         <v>6589</v>
       </c>
-      <c r="K8">
+      <c r="K8" t="n">
         <v>7126</v>
       </c>
-      <c r="L8">
+      <c r="L8" t="n">
         <v>8218</v>
       </c>
-      <c r="M8">
+      <c r="M8" t="n">
         <v>8527</v>
       </c>
-      <c r="N8">
+      <c r="N8" t="n">
         <v>8560.786088333651</v>
       </c>
-      <c r="O8">
+      <c r="O8" t="n">
         <v>9534</v>
       </c>
-      <c r="P8">
+      <c r="P8" t="n">
         <v>10978</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" t="n">
         <v>10281</v>
       </c>
-      <c r="R8">
+      <c r="R8" t="n">
         <v>10335</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="n">
         <v>10447</v>
       </c>
-      <c r="T8">
+      <c r="T8" t="n">
         <v>9741</v>
       </c>
-    </row>
-    <row r="9" spans="1:21">
-      <c r="A9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
+      <c r="U8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>厦门</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
         <v>6340.1586921309</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="n">
         <v>8249.642204929831</v>
       </c>
-      <c r="D9">
+      <c r="D9" t="n">
         <v>5256</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>7951</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="n">
         <v>8883</v>
       </c>
-      <c r="G9">
+      <c r="G9" t="n">
         <v>10555.6569648301</v>
       </c>
-      <c r="H9">
+      <c r="H9" t="n">
         <v>12280.4563629908</v>
       </c>
-      <c r="I9">
+      <c r="I9" t="n">
         <v>13625</v>
       </c>
-      <c r="J9">
+      <c r="J9" t="n">
         <v>15378</v>
       </c>
-      <c r="K9">
+      <c r="K9" t="n">
         <v>16122</v>
       </c>
-      <c r="L9">
+      <c r="L9" t="n">
         <v>20021</v>
       </c>
-      <c r="M9">
+      <c r="M9" t="n">
         <v>22599</v>
       </c>
-      <c r="N9">
+      <c r="N9" t="n">
         <v>20906.9269527358</v>
       </c>
-      <c r="O9">
+      <c r="O9" t="n">
         <v>22622</v>
       </c>
-      <c r="P9">
+      <c r="P9" t="n">
         <v>24467</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" t="n">
         <v>25004</v>
       </c>
-      <c r="R9">
+      <c r="R9" t="n">
         <v>20423</v>
       </c>
-      <c r="S9">
+      <c r="S9" t="n">
         <v>21035</v>
       </c>
-      <c r="T9">
+      <c r="T9" t="n">
         <v>15390</v>
       </c>
-    </row>
-    <row r="10" spans="1:21">
-      <c r="A10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10">
+      <c r="U9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
         <v>3110.14719579426</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="n">
         <v>3307.07907007256</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>3592</v>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>4228</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="n">
         <v>5905</v>
       </c>
-      <c r="G10">
+      <c r="G10" t="n">
         <v>6325.73931394029</v>
       </c>
-      <c r="H10">
+      <c r="H10" t="n">
         <v>6155.90810226799</v>
       </c>
-      <c r="I10">
+      <c r="I10" t="n">
         <v>6283</v>
       </c>
-      <c r="J10">
+      <c r="J10" t="n">
         <v>7157</v>
       </c>
-      <c r="K10">
+      <c r="K10" t="n">
         <v>7695</v>
       </c>
-      <c r="L10">
+      <c r="L10" t="n">
         <v>9369</v>
       </c>
-      <c r="M10">
+      <c r="M10" t="n">
         <v>10751</v>
       </c>
-      <c r="N10">
+      <c r="N10" t="n">
         <v>12146.9467667699</v>
       </c>
-      <c r="O10">
+      <c r="O10" t="n">
         <v>13365</v>
       </c>
-      <c r="P10">
+      <c r="P10" t="n">
         <v>14321</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" t="n">
         <v>13382</v>
       </c>
-      <c r="R10">
+      <c r="R10" t="n">
         <v>12415</v>
       </c>
-      <c r="S10">
+      <c r="S10" t="n">
         <v>14365</v>
       </c>
-      <c r="T10">
+      <c r="T10" t="n">
         <v>11652</v>
       </c>
-    </row>
-    <row r="11" spans="1:21">
-      <c r="A11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
+      <c r="U10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
         <v>2367.72943207356</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="n">
         <v>2595.98685925941</v>
       </c>
-      <c r="D11">
+      <c r="D11" t="n">
         <v>2731</v>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>3887</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="n">
         <v>4105</v>
       </c>
-      <c r="G11">
+      <c r="G11" t="n">
         <v>4367.46350327632</v>
       </c>
-      <c r="H11">
+      <c r="H11" t="n">
         <v>5445.13657588794</v>
       </c>
-      <c r="I11">
+      <c r="I11" t="n">
         <v>5233</v>
       </c>
-      <c r="J11">
+      <c r="J11" t="n">
         <v>5474</v>
       </c>
-      <c r="K11">
+      <c r="K11" t="n">
         <v>5193</v>
       </c>
-      <c r="L11">
+      <c r="L11" t="n">
         <v>6425</v>
       </c>
-      <c r="M11">
+      <c r="M11" t="n">
         <v>6510</v>
       </c>
-      <c r="N11">
+      <c r="N11" t="n">
         <v>8345.539815536769</v>
       </c>
-      <c r="O11">
+      <c r="O11" t="n">
         <v>10042</v>
       </c>
-      <c r="P11">
+      <c r="P11" t="n">
         <v>11001</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" t="n">
         <v>10797</v>
       </c>
-      <c r="R11">
+      <c r="R11" t="n">
         <v>11072</v>
       </c>
-      <c r="S11">
+      <c r="S11" t="n">
         <v>10855</v>
       </c>
-      <c r="T11">
+      <c r="T11" t="n">
         <v>10447</v>
       </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12">
+      <c r="U11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>哈尔滨</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
         <v>2702.92584144576</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="n">
         <v>3053.44218802469</v>
       </c>
-      <c r="D12">
+      <c r="D12" t="n">
         <v>3793</v>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>4226</v>
       </c>
-      <c r="F12">
+      <c r="F12" t="n">
         <v>5333</v>
       </c>
-      <c r="G12">
+      <c r="G12" t="n">
         <v>5398.19040412679</v>
       </c>
-      <c r="H12">
+      <c r="H12" t="n">
         <v>5517.64956475528</v>
       </c>
-      <c r="I12">
+      <c r="I12" t="n">
         <v>6194</v>
       </c>
-      <c r="J12">
+      <c r="J12" t="n">
         <v>6182</v>
       </c>
-      <c r="K12">
+      <c r="K12" t="n">
         <v>6419</v>
       </c>
-      <c r="L12">
+      <c r="L12" t="n">
         <v>6680</v>
       </c>
-      <c r="M12">
+      <c r="M12" t="n">
         <v>8339</v>
       </c>
-      <c r="N12">
+      <c r="N12" t="n">
         <v>9208.297690211481</v>
       </c>
-      <c r="O12">
+      <c r="O12" t="n">
         <v>9920</v>
       </c>
-      <c r="P12">
+      <c r="P12" t="n">
         <v>9467</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" t="n">
         <v>8760</v>
       </c>
-      <c r="R12">
+      <c r="R12" t="n">
         <v>8408</v>
       </c>
-      <c r="S12">
+      <c r="S12" t="n">
         <v>8586</v>
       </c>
-      <c r="T12">
+      <c r="T12" t="n">
         <v>8611</v>
       </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13">
+      <c r="U12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>大连</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>4525.22760619953</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="n">
         <v>5567.76045518345</v>
       </c>
-      <c r="D13">
+      <c r="D13" t="n">
         <v>5774</v>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>6249</v>
       </c>
-      <c r="F13">
+      <c r="F13" t="n">
         <v>7044</v>
       </c>
-      <c r="G13">
+      <c r="G13" t="n">
         <v>8052.00401577957</v>
       </c>
-      <c r="H13">
+      <c r="H13" t="n">
         <v>8003.54137231104</v>
       </c>
-      <c r="I13">
+      <c r="I13" t="n">
         <v>8263</v>
       </c>
-      <c r="J13">
+      <c r="J13" t="n">
         <v>9216</v>
       </c>
-      <c r="K13">
+      <c r="K13" t="n">
         <v>8929</v>
       </c>
-      <c r="L13">
+      <c r="L13" t="n">
         <v>9354</v>
       </c>
-      <c r="M13">
+      <c r="M13" t="n">
         <v>10315</v>
       </c>
-      <c r="N13">
+      <c r="N13" t="n">
         <v>11546.299028926</v>
       </c>
-      <c r="O13">
+      <c r="O13" t="n">
         <v>11972</v>
       </c>
-      <c r="P13">
+      <c r="P13" t="n">
         <v>13302</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" t="n">
         <v>13746</v>
       </c>
-      <c r="R13">
+      <c r="R13" t="n">
         <v>12506</v>
       </c>
-      <c r="S13">
+      <c r="S13" t="n">
         <v>11676</v>
       </c>
-      <c r="T13">
+      <c r="T13" t="n">
         <v>11074</v>
       </c>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14">
+      <c r="U13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
         <v>4773.53739041535</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="n">
         <v>5811.1113887825</v>
       </c>
-      <c r="D14">
+      <c r="D14" t="n">
         <v>6015</v>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>6886</v>
       </c>
-      <c r="F14">
+      <c r="F14" t="n">
         <v>8230</v>
       </c>
-      <c r="G14">
+      <c r="G14" t="n">
         <v>8744.771551192969</v>
       </c>
-      <c r="H14">
+      <c r="H14" t="n">
         <v>8217.67315656955</v>
       </c>
-      <c r="I14">
+      <c r="I14" t="n">
         <v>8746</v>
       </c>
-      <c r="J14">
+      <c r="J14" t="n">
         <v>9219</v>
       </c>
-      <c r="K14">
+      <c r="K14" t="n">
         <v>10107</v>
       </c>
-      <c r="L14">
+      <c r="L14" t="n">
         <v>12830</v>
       </c>
-      <c r="M14">
+      <c r="M14" t="n">
         <v>15331</v>
       </c>
-      <c r="N14">
+      <c r="N14" t="n">
         <v>16054.6385261175</v>
       </c>
-      <c r="O14">
+      <c r="O14" t="n">
         <v>15380</v>
       </c>
-      <c r="P14">
+      <c r="P14" t="n">
         <v>16172</v>
       </c>
-      <c r="Q14">
+      <c r="Q14" t="n">
         <v>16182</v>
       </c>
-      <c r="R14">
+      <c r="R14" t="n">
         <v>15572</v>
       </c>
-      <c r="S14">
+      <c r="S14" t="n">
         <v>16087</v>
       </c>
-      <c r="T14">
+      <c r="T14" t="n">
         <v>14819</v>
       </c>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15">
+      <c r="U14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>太原</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
         <v>3578.51031302693</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="n">
         <v>3862.36903273337</v>
       </c>
-      <c r="D15">
+      <c r="D15" t="n">
         <v>4013</v>
       </c>
-      <c r="E15">
+      <c r="E15" t="n">
         <v>4830</v>
       </c>
-      <c r="F15">
+      <c r="F15" t="n">
         <v>7244</v>
       </c>
-      <c r="G15">
+      <c r="G15" t="n">
         <v>6816.03291364793</v>
       </c>
-      <c r="H15">
+      <c r="H15" t="n">
         <v>6805.38990550302</v>
       </c>
-      <c r="I15">
+      <c r="I15" t="n">
         <v>7158</v>
       </c>
-      <c r="J15">
+      <c r="J15" t="n">
         <v>7651</v>
       </c>
-      <c r="K15">
+      <c r="K15" t="n">
         <v>7508</v>
       </c>
-      <c r="L15">
+      <c r="L15" t="n">
         <v>7667</v>
       </c>
-      <c r="M15">
+      <c r="M15" t="n">
         <v>9017</v>
       </c>
-      <c r="N15">
+      <c r="N15" t="n">
         <v>11058.5994812611</v>
       </c>
-      <c r="O15">
+      <c r="O15" t="n">
         <v>11181</v>
       </c>
-      <c r="P15">
+      <c r="P15" t="n">
         <v>10759</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" t="n">
         <v>10244</v>
       </c>
-      <c r="R15">
+      <c r="R15" t="n">
         <v>9835</v>
       </c>
-      <c r="S15">
+      <c r="S15" t="n">
         <v>10193</v>
       </c>
-      <c r="T15">
+      <c r="T15" t="n">
         <v>11437</v>
       </c>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16">
+      <c r="U15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>宁波</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
         <v>5437.48572163825</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="n">
         <v>6251.49314115379</v>
       </c>
-      <c r="D16">
+      <c r="D16" t="n">
         <v>7224</v>
       </c>
-      <c r="E16">
+      <c r="E16" t="n">
         <v>8992</v>
       </c>
-      <c r="F16">
+      <c r="F16" t="n">
         <v>11224</v>
       </c>
-      <c r="G16">
+      <c r="G16" t="n">
         <v>11031.7272353815</v>
       </c>
-      <c r="H16">
+      <c r="H16" t="n">
         <v>11239.839970804</v>
       </c>
-      <c r="I16">
+      <c r="I16" t="n">
         <v>11100</v>
       </c>
-      <c r="J16">
+      <c r="J16" t="n">
         <v>10745</v>
       </c>
-      <c r="K16">
+      <c r="K16" t="n">
         <v>10708</v>
       </c>
-      <c r="L16">
+      <c r="L16" t="n">
         <v>11228</v>
       </c>
-      <c r="M16">
+      <c r="M16" t="n">
         <v>13324</v>
       </c>
-      <c r="N16">
+      <c r="N16" t="n">
         <v>15142.0489034197</v>
       </c>
-      <c r="O16">
+      <c r="O16" t="n">
         <v>15065</v>
       </c>
-      <c r="P16">
+      <c r="P16" t="n">
         <v>16411</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" t="n">
         <v>18782</v>
       </c>
-      <c r="R16">
+      <c r="R16" t="n">
         <v>17165</v>
       </c>
-      <c r="S16">
+      <c r="S16" t="n">
         <v>18025</v>
       </c>
-      <c r="T16">
+      <c r="T16" t="n">
         <v>15582</v>
       </c>
-    </row>
-    <row r="17" spans="1:20">
-      <c r="A17" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17">
+      <c r="U16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
         <v>6547.92046255852</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="n">
         <v>8673.06731290298</v>
       </c>
-      <c r="D17">
+      <c r="D17" t="n">
         <v>9123</v>
       </c>
-      <c r="E17">
+      <c r="E17" t="n">
         <v>9351</v>
       </c>
-      <c r="F17">
+      <c r="F17" t="n">
         <v>11921</v>
       </c>
-      <c r="G17">
+      <c r="G17" t="n">
         <v>12103.5210922592</v>
       </c>
-      <c r="H17">
+      <c r="H17" t="n">
         <v>13162.6727828182</v>
       </c>
-      <c r="I17">
+      <c r="I17" t="n">
         <v>15330</v>
       </c>
-      <c r="J17">
+      <c r="J17" t="n">
         <v>15719</v>
       </c>
-      <c r="K17">
+      <c r="K17" t="n">
         <v>14612</v>
       </c>
-      <c r="L17">
+      <c r="L17" t="n">
         <v>16384</v>
       </c>
-      <c r="M17">
+      <c r="M17" t="n">
         <v>17633</v>
       </c>
-      <c r="N17">
+      <c r="N17" t="n">
         <v>20013.6008031086</v>
       </c>
-      <c r="O17">
+      <c r="O17" t="n">
         <v>22363</v>
       </c>
-      <c r="P17">
+      <c r="P17" t="n">
         <v>25056</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" t="n">
         <v>28034</v>
       </c>
-      <c r="R17">
+      <c r="R17" t="n">
         <v>26356</v>
       </c>
-      <c r="S17">
+      <c r="S17" t="n">
         <v>29040</v>
       </c>
-      <c r="T17">
+      <c r="T17" t="n">
         <v>26865</v>
       </c>
-    </row>
-    <row r="18" spans="1:20">
-      <c r="A18" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18">
+      <c r="U17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>成都</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
         <v>3645.71746734544</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="n">
         <v>4276.08929102369</v>
       </c>
-      <c r="D18">
+      <c r="D18" t="n">
         <v>4857</v>
       </c>
-      <c r="E18">
+      <c r="E18" t="n">
         <v>4925</v>
       </c>
-      <c r="F18">
+      <c r="F18" t="n">
         <v>5937</v>
       </c>
-      <c r="G18">
+      <c r="G18" t="n">
         <v>6716.71303371431</v>
       </c>
-      <c r="H18">
+      <c r="H18" t="n">
         <v>7288.24069375895</v>
       </c>
-      <c r="I18">
+      <c r="I18" t="n">
         <v>7197</v>
       </c>
-      <c r="J18">
+      <c r="J18" t="n">
         <v>7032</v>
       </c>
-      <c r="K18">
+      <c r="K18" t="n">
         <v>6875</v>
       </c>
-      <c r="L18">
+      <c r="L18" t="n">
         <v>7504</v>
       </c>
-      <c r="M18">
+      <c r="M18" t="n">
         <v>8733</v>
       </c>
-      <c r="N18">
+      <c r="N18" t="n">
         <v>9866.596645843631</v>
       </c>
-      <c r="O18">
+      <c r="O18" t="n">
         <v>10867</v>
       </c>
-      <c r="P18">
+      <c r="P18" t="n">
         <v>12148</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" t="n">
         <v>12858</v>
       </c>
-      <c r="R18">
+      <c r="R18" t="n">
         <v>14243</v>
       </c>
-      <c r="S18">
+      <c r="S18" t="n">
         <v>17329</v>
       </c>
-      <c r="T18">
+      <c r="T18" t="n">
         <v>15596</v>
       </c>
-    </row>
-    <row r="19" spans="1:20">
-      <c r="A19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20">
-      <c r="A20" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20">
+      <c r="U18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>拉萨</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>昆明</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
         <v>2903.31908754546</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="n">
         <v>3108.12174057031</v>
       </c>
-      <c r="D20">
+      <c r="D20" t="n">
         <v>3750</v>
       </c>
-      <c r="E20">
+      <c r="E20" t="n">
         <v>3807</v>
       </c>
-      <c r="F20">
+      <c r="F20" t="n">
         <v>3660</v>
       </c>
-      <c r="G20">
+      <c r="G20" t="n">
         <v>4715.22810619893</v>
       </c>
-      <c r="H20">
+      <c r="H20" t="n">
         <v>5744.68313788363</v>
       </c>
-      <c r="I20">
+      <c r="I20" t="n">
         <v>5795</v>
       </c>
-      <c r="J20">
+      <c r="J20" t="n">
         <v>6384</v>
       </c>
-      <c r="K20">
+      <c r="K20" t="n">
         <v>7393</v>
       </c>
-      <c r="L20">
+      <c r="L20" t="n">
         <v>7030</v>
       </c>
-      <c r="M20">
+      <c r="M20" t="n">
         <v>8010</v>
       </c>
-      <c r="N20">
+      <c r="N20" t="n">
         <v>10472.1956520248</v>
       </c>
-      <c r="O20">
+      <c r="O20" t="n">
         <v>11197</v>
       </c>
-      <c r="P20">
+      <c r="P20" t="n">
         <v>11325</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" t="n">
         <v>10852</v>
       </c>
-      <c r="R20">
+      <c r="R20" t="n">
         <v>9720</v>
       </c>
-      <c r="S20">
+      <c r="S20" t="n">
         <v>9275</v>
       </c>
-      <c r="T20">
+      <c r="T20" t="n">
         <v>8821</v>
       </c>
-    </row>
-    <row r="21" spans="1:20">
-      <c r="A21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21">
+      <c r="U20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
         <v>6218.29174047041</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="n">
         <v>7615.67259126513</v>
       </c>
-      <c r="D21">
+      <c r="D21" t="n">
         <v>8409</v>
       </c>
-      <c r="E21">
+      <c r="E21" t="n">
         <v>10555</v>
       </c>
-      <c r="F21">
+      <c r="F21" t="n">
         <v>14132</v>
       </c>
-      <c r="G21">
+      <c r="G21" t="n">
         <v>13285.9699056065</v>
       </c>
-      <c r="H21">
+      <c r="H21" t="n">
         <v>13447.3764054627</v>
       </c>
-      <c r="I21">
+      <c r="I21" t="n">
         <v>15022</v>
       </c>
-      <c r="J21">
+      <c r="J21" t="n">
         <v>13896</v>
       </c>
-      <c r="K21">
+      <c r="K21" t="n">
         <v>14422</v>
       </c>
-      <c r="L21">
+      <c r="L21" t="n">
         <v>15753</v>
       </c>
-      <c r="M21">
+      <c r="M21" t="n">
         <v>20354</v>
       </c>
-      <c r="N21">
+      <c r="N21" t="n">
         <v>23917.2932151379</v>
       </c>
-      <c r="O21">
+      <c r="O21" t="n">
         <v>25922</v>
       </c>
-      <c r="P21">
+      <c r="P21" t="n">
         <v>27043</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" t="n">
         <v>29465</v>
       </c>
-      <c r="R21">
+      <c r="R21" t="n">
         <v>32522</v>
       </c>
-      <c r="S21">
+      <c r="S21" t="n">
         <v>31536</v>
       </c>
-      <c r="T21">
+      <c r="T21" t="n">
         <v>28530</v>
       </c>
-    </row>
-    <row r="22" spans="1:20">
-      <c r="A22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22">
+      <c r="U21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>武汉</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
         <v>3689.64079623612</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="n">
         <v>4664.02745010691</v>
       </c>
-      <c r="D22">
+      <c r="D22" t="n">
         <v>4781</v>
       </c>
-      <c r="E22">
+      <c r="E22" t="n">
         <v>5329</v>
       </c>
-      <c r="F22">
+      <c r="F22" t="n">
         <v>5746</v>
       </c>
-      <c r="G22">
+      <c r="G22" t="n">
         <v>7192.89982687605</v>
       </c>
-      <c r="H22">
+      <c r="H22" t="n">
         <v>7344.05270283354</v>
       </c>
-      <c r="I22">
+      <c r="I22" t="n">
         <v>7717</v>
       </c>
-      <c r="J22">
+      <c r="J22" t="n">
         <v>7951</v>
       </c>
-      <c r="K22">
+      <c r="K22" t="n">
         <v>8556</v>
       </c>
-      <c r="L22">
+      <c r="L22" t="n">
         <v>10048</v>
       </c>
-      <c r="M22">
+      <c r="M22" t="n">
         <v>11744</v>
       </c>
-      <c r="N22">
+      <c r="N22" t="n">
         <v>13108.2537133675</v>
       </c>
-      <c r="O22">
+      <c r="O22" t="n">
         <v>14258</v>
       </c>
-      <c r="P22">
+      <c r="P22" t="n">
         <v>14244</v>
       </c>
-      <c r="Q22">
+      <c r="Q22" t="n">
         <v>15067</v>
       </c>
-      <c r="R22">
+      <c r="R22" t="n">
         <v>14048</v>
       </c>
-      <c r="S22">
+      <c r="S22" t="n">
         <v>14305</v>
       </c>
-      <c r="T22">
+      <c r="T22" t="n">
         <v>12771</v>
       </c>
-    </row>
-    <row r="23" spans="1:20">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23">
+      <c r="U22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>沈阳</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
         <v>3376.17045594879</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="n">
         <v>3698.98037875633</v>
       </c>
-      <c r="D23">
+      <c r="D23" t="n">
         <v>4127</v>
       </c>
-      <c r="E23">
+      <c r="E23" t="n">
         <v>4464</v>
       </c>
-      <c r="F23">
+      <c r="F23" t="n">
         <v>5411</v>
       </c>
-      <c r="G23">
+      <c r="G23" t="n">
         <v>5884.18203693483</v>
       </c>
-      <c r="H23">
+      <c r="H23" t="n">
         <v>6321.25992133469</v>
       </c>
-      <c r="I23">
+      <c r="I23" t="n">
         <v>6348</v>
       </c>
-      <c r="J23">
+      <c r="J23" t="n">
         <v>6217</v>
       </c>
-      <c r="K23">
+      <c r="K23" t="n">
         <v>6861</v>
       </c>
-      <c r="L23">
+      <c r="L23" t="n">
         <v>7128</v>
       </c>
-      <c r="M23">
+      <c r="M23" t="n">
         <v>8062</v>
       </c>
-      <c r="N23">
+      <c r="N23" t="n">
         <v>8892.07283156306</v>
       </c>
-      <c r="O23">
+      <c r="O23" t="n">
         <v>10192</v>
       </c>
-      <c r="P23">
+      <c r="P23" t="n">
         <v>11376</v>
       </c>
-      <c r="Q23">
+      <c r="Q23" t="n">
         <v>11591</v>
       </c>
-      <c r="R23">
+      <c r="R23" t="n">
         <v>10798</v>
       </c>
-      <c r="S23">
+      <c r="S23" t="n">
         <v>10749</v>
       </c>
-      <c r="T23">
+      <c r="T23" t="n">
         <v>10542</v>
       </c>
-    </row>
-    <row r="24" spans="1:20">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24">
+      <c r="U23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
         <v>3524.99341307899</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="n">
         <v>3776.27989587965</v>
       </c>
-      <c r="D24">
+      <c r="D24" t="n">
         <v>4179</v>
       </c>
-      <c r="E24">
+      <c r="E24" t="n">
         <v>4897</v>
       </c>
-      <c r="F24">
+      <c r="F24" t="n">
         <v>6259</v>
       </c>
-      <c r="G24">
+      <c r="G24" t="n">
         <v>6698.35710577542</v>
       </c>
-      <c r="H24">
+      <c r="H24" t="n">
         <v>6832.43506152864</v>
       </c>
-      <c r="I24">
+      <c r="I24" t="n">
         <v>7152</v>
       </c>
-      <c r="J24">
+      <c r="J24" t="n">
         <v>7369</v>
       </c>
-      <c r="K24">
+      <c r="K24" t="n">
         <v>7686</v>
       </c>
-      <c r="L24">
+      <c r="L24" t="n">
         <v>8247</v>
       </c>
-      <c r="M24">
+      <c r="M24" t="n">
         <v>9644</v>
       </c>
-      <c r="N24">
+      <c r="N24" t="n">
         <v>11930.0048952377</v>
       </c>
-      <c r="O24">
+      <c r="O24" t="n">
         <v>11438</v>
       </c>
-      <c r="P24">
+      <c r="P24" t="n">
         <v>11768</v>
       </c>
-      <c r="Q24">
+      <c r="Q24" t="n">
         <v>12640</v>
       </c>
-      <c r="R24">
+      <c r="R24" t="n">
         <v>12195</v>
       </c>
-      <c r="S24">
+      <c r="S24" t="n">
         <v>13275</v>
       </c>
-      <c r="T24">
+      <c r="T24" t="n">
         <v>11660</v>
       </c>
-    </row>
-    <row r="25" spans="1:20">
-      <c r="A25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B25">
+      <c r="U24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>海口</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>2785.80228391902</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="n">
         <v>3515.72321509757</v>
       </c>
-      <c r="D25">
+      <c r="D25" t="n">
         <v>4533</v>
       </c>
-      <c r="E25">
+      <c r="E25" t="n">
         <v>5344</v>
       </c>
-      <c r="F25">
+      <c r="F25" t="n">
         <v>8015</v>
       </c>
-      <c r="G25">
+      <c r="G25" t="n">
         <v>6634.56032922672</v>
       </c>
-      <c r="H25">
+      <c r="H25" t="n">
         <v>6821.26188748568</v>
       </c>
-      <c r="I25">
+      <c r="I25" t="n">
         <v>7423</v>
       </c>
-      <c r="J25">
+      <c r="J25" t="n">
         <v>7903</v>
       </c>
-      <c r="K25">
+      <c r="K25" t="n">
         <v>7948</v>
       </c>
-      <c r="L25">
+      <c r="L25" t="n">
         <v>9043</v>
       </c>
-      <c r="M25">
+      <c r="M25" t="n">
         <v>11988</v>
       </c>
-      <c r="N25">
+      <c r="N25" t="n">
         <v>13233.0633613746</v>
       </c>
-      <c r="O25">
+      <c r="O25" t="n">
         <v>15385</v>
       </c>
-      <c r="P25">
+      <c r="P25" t="n">
         <v>15837</v>
       </c>
-      <c r="Q25">
+      <c r="Q25" t="n">
         <v>15825</v>
       </c>
-      <c r="R25">
+      <c r="R25" t="n">
         <v>16018</v>
       </c>
-      <c r="S25">
+      <c r="S25" t="n">
         <v>15826</v>
       </c>
-      <c r="T25">
+      <c r="T25" t="n">
         <v>12294</v>
       </c>
-    </row>
-    <row r="26" spans="1:20">
-      <c r="A26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B26">
+      <c r="U25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
         <v>9385.339968160841</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="n">
         <v>14049.6913946096</v>
       </c>
-      <c r="D26">
+      <c r="D26" t="n">
         <v>12665</v>
       </c>
-      <c r="E26">
+      <c r="E26" t="n">
         <v>14615</v>
       </c>
-      <c r="F26">
+      <c r="F26" t="n">
         <v>19170</v>
       </c>
-      <c r="G26">
+      <c r="G26" t="n">
         <v>21350.1325245679</v>
       </c>
-      <c r="H26">
+      <c r="H26" t="n">
         <v>19589.8187524794</v>
       </c>
-      <c r="I26">
+      <c r="I26" t="n">
         <v>24402</v>
       </c>
-      <c r="J26">
+      <c r="J26" t="n">
         <v>24723</v>
       </c>
-      <c r="K26">
+      <c r="K26" t="n">
         <v>33942</v>
       </c>
-      <c r="L26">
+      <c r="L26" t="n">
         <v>45146</v>
       </c>
-      <c r="M26">
+      <c r="M26" t="n">
         <v>47936</v>
       </c>
-      <c r="N26">
+      <c r="N26" t="n">
         <v>54132.442008163</v>
       </c>
-      <c r="O26">
+      <c r="O26" t="n">
         <v>55797</v>
       </c>
-      <c r="P26">
+      <c r="P26" t="n">
         <v>56829</v>
       </c>
-      <c r="Q26">
+      <c r="Q26" t="n">
         <v>58593</v>
       </c>
-      <c r="R26">
+      <c r="R26" t="n">
         <v>51580</v>
       </c>
-      <c r="S26">
+      <c r="S26" t="n">
         <v>45524</v>
       </c>
-      <c r="T26">
+      <c r="T26" t="n">
         <v>42976</v>
       </c>
-    </row>
-    <row r="27" spans="1:20">
-      <c r="A27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B27">
+      <c r="U26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>石家庄</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
         <v>2068.4284949935</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="n">
         <v>2451.65217872947</v>
       </c>
-      <c r="D27">
+      <c r="D27" t="n">
         <v>2610</v>
       </c>
-      <c r="E27">
+      <c r="E27" t="n">
         <v>3765</v>
       </c>
-      <c r="F27">
+      <c r="F27" t="n">
         <v>3881</v>
       </c>
-      <c r="G27">
+      <c r="G27" t="n">
         <v>4740.49655169722</v>
       </c>
-      <c r="H27">
+      <c r="H27" t="n">
         <v>4930.93636790194</v>
       </c>
-      <c r="I27">
+      <c r="I27" t="n">
         <v>5503</v>
       </c>
-      <c r="J27">
+      <c r="J27" t="n">
         <v>5737</v>
       </c>
-      <c r="K27">
+      <c r="K27" t="n">
         <v>8601</v>
       </c>
-      <c r="L27">
+      <c r="L27" t="n">
         <v>8281</v>
       </c>
-      <c r="M27">
+      <c r="M27" t="n">
         <v>10170</v>
       </c>
-      <c r="N27">
+      <c r="N27" t="n">
         <v>10452.4227823225</v>
       </c>
-      <c r="O27">
+      <c r="O27" t="n">
         <v>9309</v>
       </c>
-      <c r="P27">
+      <c r="P27" t="n">
         <v>9869</v>
       </c>
-      <c r="Q27">
+      <c r="Q27" t="n">
         <v>10269</v>
       </c>
-      <c r="R27">
+      <c r="R27" t="n">
         <v>9925</v>
       </c>
-      <c r="S27">
+      <c r="S27" t="n">
         <v>10599</v>
       </c>
-      <c r="T27">
+      <c r="T27" t="n">
         <v>11521</v>
       </c>
-    </row>
-    <row r="28" spans="1:20">
-      <c r="A28" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28">
+      <c r="U27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>福州</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
         <v>4396.50126470283</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="n">
         <v>5178.68128804424</v>
       </c>
-      <c r="D28">
+      <c r="D28" t="n">
         <v>5516</v>
       </c>
-      <c r="E28">
+      <c r="E28" t="n">
         <v>6625</v>
       </c>
-      <c r="F28">
+      <c r="F28" t="n">
         <v>8414</v>
       </c>
-      <c r="G28">
+      <c r="G28" t="n">
         <v>10178.145474629</v>
       </c>
-      <c r="H28">
+      <c r="H28" t="n">
         <v>11188.3045249894</v>
       </c>
-      <c r="I28">
+      <c r="I28" t="n">
         <v>11236</v>
       </c>
-      <c r="J28">
+      <c r="J28" t="n">
         <v>10719</v>
       </c>
-      <c r="K28">
+      <c r="K28" t="n">
         <v>11653</v>
       </c>
-      <c r="L28">
+      <c r="L28" t="n">
         <v>11089</v>
       </c>
-      <c r="M28">
+      <c r="M28" t="n">
         <v>11057</v>
       </c>
-      <c r="N28">
+      <c r="N28" t="n">
         <v>13530.2954317511</v>
       </c>
-      <c r="O28">
+      <c r="O28" t="n">
         <v>13656</v>
       </c>
-      <c r="P28">
+      <c r="P28" t="n">
         <v>13520</v>
       </c>
-      <c r="Q28">
+      <c r="Q28" t="n">
         <v>14149</v>
       </c>
-      <c r="R28">
+      <c r="R28" t="n">
         <v>12381</v>
       </c>
-      <c r="S28">
+      <c r="S28" t="n">
         <v>12629</v>
       </c>
-      <c r="T28">
+      <c r="T28" t="n">
         <v>13405</v>
       </c>
-    </row>
-    <row r="29" spans="1:20">
-      <c r="A29" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B29">
+      <c r="U28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>西宁</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
         <v>2021.98749933062</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="n">
         <v>2420.96083137045</v>
       </c>
-      <c r="D29">
+      <c r="D29" t="n">
         <v>2900</v>
       </c>
-      <c r="E29">
+      <c r="E29" t="n">
         <v>2900</v>
       </c>
-      <c r="F29">
+      <c r="F29" t="n">
         <v>3328</v>
       </c>
-      <c r="G29">
+      <c r="G29" t="n">
         <v>3646.3427352239</v>
       </c>
-      <c r="H29">
+      <c r="H29" t="n">
         <v>4718.33615291848</v>
       </c>
-      <c r="I29">
+      <c r="I29" t="n">
         <v>4628</v>
       </c>
-      <c r="J29">
+      <c r="J29" t="n">
         <v>5753</v>
       </c>
-      <c r="K29">
+      <c r="K29" t="n">
         <v>5758</v>
       </c>
-      <c r="L29">
+      <c r="L29" t="n">
         <v>5910</v>
       </c>
-      <c r="M29">
+      <c r="M29" t="n">
         <v>6642</v>
       </c>
-      <c r="N29">
+      <c r="N29" t="n">
         <v>7313.45862335095</v>
       </c>
-      <c r="O29">
+      <c r="O29" t="n">
         <v>8989</v>
       </c>
-      <c r="P29">
+      <c r="P29" t="n">
         <v>9628</v>
       </c>
-      <c r="Q29">
+      <c r="Q29" t="n">
         <v>9173</v>
       </c>
-      <c r="R29">
+      <c r="R29" t="n">
         <v>8943</v>
       </c>
-      <c r="S29">
+      <c r="S29" t="n">
         <v>8882</v>
       </c>
-      <c r="T29">
+      <c r="T29" t="n">
         <v>8361</v>
       </c>
-    </row>
-    <row r="30" spans="1:20">
-      <c r="A30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30">
+      <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>西安</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
         <v>3316.88446970154</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="n">
         <v>3379.07794010887</v>
       </c>
-      <c r="D30">
+      <c r="D30" t="n">
         <v>3906</v>
       </c>
-      <c r="E30">
+      <c r="E30" t="n">
         <v>3890</v>
       </c>
-      <c r="F30">
+      <c r="F30" t="n">
         <v>4453</v>
       </c>
-      <c r="G30">
+      <c r="G30" t="n">
         <v>6155.5981210251</v>
       </c>
-      <c r="H30">
+      <c r="H30" t="n">
         <v>6634.31598335468</v>
       </c>
-      <c r="I30">
+      <c r="I30" t="n">
         <v>6716</v>
       </c>
-      <c r="J30">
+      <c r="J30" t="n">
         <v>6465</v>
       </c>
-      <c r="K30">
+      <c r="K30" t="n">
         <v>6501</v>
       </c>
-      <c r="L30">
+      <c r="L30" t="n">
         <v>6602</v>
       </c>
-      <c r="M30">
+      <c r="M30" t="n">
         <v>8513</v>
       </c>
-      <c r="N30">
+      <c r="N30" t="n">
         <v>10171.0134542708</v>
       </c>
-      <c r="O30">
+      <c r="O30" t="n">
         <v>11480</v>
       </c>
-      <c r="P30">
+      <c r="P30" t="n">
         <v>13358</v>
       </c>
-      <c r="Q30">
+      <c r="Q30" t="n">
         <v>14657</v>
       </c>
-      <c r="R30">
+      <c r="R30" t="n">
         <v>14713</v>
       </c>
-      <c r="S30">
+      <c r="S30" t="n">
         <v>15836</v>
       </c>
-      <c r="T30">
+      <c r="T30" t="n">
         <v>14849</v>
       </c>
-    </row>
-    <row r="31" spans="1:20">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B31">
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
         <v>2372.65862589521</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="n">
         <v>2901.62517434696</v>
       </c>
-      <c r="D31">
+      <c r="D31" t="n">
         <v>3149</v>
       </c>
-      <c r="E31">
+      <c r="E31" t="n">
         <v>3762</v>
       </c>
-      <c r="F31">
+      <c r="F31" t="n">
         <v>4410</v>
       </c>
-      <c r="G31">
+      <c r="G31" t="n">
         <v>5069.51968208393</v>
       </c>
-      <c r="H31">
+      <c r="H31" t="n">
         <v>4846.13761760905</v>
       </c>
-      <c r="I31">
+      <c r="I31" t="n">
         <v>5025</v>
       </c>
-      <c r="J31">
+      <c r="J31" t="n">
         <v>5608</v>
       </c>
-      <c r="K31">
+      <c r="K31" t="n">
         <v>6029</v>
       </c>
-      <c r="L31">
+      <c r="L31" t="n">
         <v>5957</v>
       </c>
-      <c r="M31">
+      <c r="M31" t="n">
         <v>7269</v>
       </c>
-      <c r="N31">
+      <c r="N31" t="n">
         <v>9360.755125705349</v>
       </c>
-      <c r="O31">
+      <c r="O31" t="n">
         <v>10451</v>
       </c>
-      <c r="P31">
+      <c r="P31" t="n">
         <v>9315</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" t="n">
         <v>9052</v>
       </c>
-      <c r="R31">
+      <c r="R31" t="n">
         <v>8879</v>
       </c>
-      <c r="S31">
+      <c r="S31" t="n">
         <v>9208</v>
       </c>
-      <c r="T31">
+      <c r="T31" t="n">
         <v>8953</v>
       </c>
-    </row>
-    <row r="32" spans="1:20">
-      <c r="A32" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B32">
+      <c r="U31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>郑州</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
         <v>2888.35790702684</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="n">
         <v>3573.59583566735</v>
       </c>
-      <c r="D32">
+      <c r="D32" t="n">
         <v>3928</v>
       </c>
-      <c r="E32">
+      <c r="E32" t="n">
         <v>4298</v>
       </c>
-      <c r="F32">
+      <c r="F32" t="n">
         <v>4957</v>
       </c>
-      <c r="G32">
+      <c r="G32" t="n">
         <v>5696.16486188626</v>
       </c>
-      <c r="H32">
+      <c r="H32" t="n">
         <v>6253.10551790766</v>
       </c>
-      <c r="I32">
+      <c r="I32" t="n">
         <v>7162</v>
       </c>
-      <c r="J32">
+      <c r="J32" t="n">
         <v>7571</v>
       </c>
-      <c r="K32">
+      <c r="K32" t="n">
         <v>7537</v>
       </c>
-      <c r="L32">
+      <c r="L32" t="n">
         <v>8163</v>
       </c>
-      <c r="M32">
+      <c r="M32" t="n">
         <v>8631</v>
       </c>
-      <c r="N32">
+      <c r="N32" t="n">
         <v>8442.615304167761</v>
       </c>
-      <c r="O32">
+      <c r="O32" t="n">
         <v>9472</v>
       </c>
-      <c r="P32">
+      <c r="P32" t="n">
         <v>9834</v>
       </c>
-      <c r="Q32">
+      <c r="Q32" t="n">
         <v>9664</v>
       </c>
-      <c r="R32">
+      <c r="R32" t="n">
         <v>8150</v>
       </c>
-      <c r="S32">
+      <c r="S32" t="n">
         <v>8619</v>
       </c>
-      <c r="T32">
+      <c r="T32" t="n">
         <v>7919</v>
       </c>
-    </row>
-    <row r="33" spans="1:20">
-      <c r="A33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B33">
+      <c r="U32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>重庆</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
         <v>2269.21434704752</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="n">
         <v>2722.58260629102</v>
       </c>
-      <c r="D33">
+      <c r="D33" t="n">
         <v>2785</v>
       </c>
-      <c r="E33">
+      <c r="E33" t="n">
         <v>3442</v>
       </c>
-      <c r="F33">
+      <c r="F33" t="n">
         <v>4281</v>
       </c>
-      <c r="G33">
+      <c r="G33" t="n">
         <v>4733.83721312657</v>
       </c>
-      <c r="H33">
+      <c r="H33" t="n">
         <v>5079.92780912311</v>
       </c>
-      <c r="I33">
+      <c r="I33" t="n">
         <v>5569</v>
       </c>
-      <c r="J33">
+      <c r="J33" t="n">
         <v>5519</v>
       </c>
-      <c r="K33">
+      <c r="K33" t="n">
         <v>5486</v>
       </c>
-      <c r="L33">
+      <c r="L33" t="n">
         <v>5485</v>
       </c>
-      <c r="M33">
+      <c r="M33" t="n">
         <v>6792</v>
       </c>
-      <c r="N33">
+      <c r="N33" t="n">
         <v>8066.85951224592</v>
       </c>
-      <c r="O33">
+      <c r="O33" t="n">
         <v>8402</v>
       </c>
-      <c r="P33">
+      <c r="P33" t="n">
         <v>8255</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" t="n">
         <v>8699</v>
       </c>
-      <c r="R33">
+      <c r="R33" t="n">
         <v>7132</v>
       </c>
-      <c r="S33">
+      <c r="S33" t="n">
         <v>6888</v>
       </c>
-      <c r="T33">
+      <c r="T33" t="n">
         <v>6898</v>
       </c>
-    </row>
-    <row r="34" spans="1:20">
-      <c r="A34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34">
+      <c r="U33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
         <v>2398.55993399697</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="n">
         <v>2407.90144563976</v>
       </c>
-      <c r="D34">
+      <c r="D34" t="n">
         <v>2828</v>
       </c>
-      <c r="E34">
+      <c r="E34" t="n">
         <v>3523</v>
       </c>
-      <c r="F34">
+      <c r="F34" t="n">
         <v>3792</v>
       </c>
-      <c r="G34">
+      <c r="G34" t="n">
         <v>4375.82293227371</v>
       </c>
-      <c r="H34">
+      <c r="H34" t="n">
         <v>4574.53787914121</v>
       </c>
-      <c r="I34">
+      <c r="I34" t="n">
         <v>4856</v>
       </c>
-      <c r="J34">
+      <c r="J34" t="n">
         <v>4451</v>
       </c>
-      <c r="K34">
+      <c r="K34" t="n">
         <v>4947</v>
       </c>
-      <c r="L34">
+      <c r="L34" t="n">
         <v>4790</v>
       </c>
-      <c r="M34">
+      <c r="M34" t="n">
         <v>5177</v>
       </c>
-      <c r="N34">
+      <c r="N34" t="n">
         <v>5874.82440035853</v>
       </c>
-      <c r="O34">
+      <c r="O34" t="n">
         <v>6440</v>
       </c>
-      <c r="P34">
+      <c r="P34" t="n">
         <v>7238</v>
       </c>
-      <c r="Q34">
+      <c r="Q34" t="n">
         <v>7648</v>
       </c>
-      <c r="R34">
+      <c r="R34" t="n">
         <v>8392</v>
       </c>
-      <c r="S34">
+      <c r="S34" t="n">
         <v>8565</v>
       </c>
-      <c r="T34">
+      <c r="T34" t="n">
         <v>8336</v>
       </c>
-    </row>
-    <row r="35" spans="1:20">
-      <c r="A35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B35">
+      <c r="U34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>长春</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
         <v>2558.39023429578</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="n">
         <v>3249.64400634366</v>
       </c>
-      <c r="D35">
+      <c r="D35" t="n">
         <v>3489</v>
       </c>
-      <c r="E35">
+      <c r="E35" t="n">
         <v>4142</v>
       </c>
-      <c r="F35">
+      <c r="F35" t="n">
         <v>5178</v>
       </c>
-      <c r="G35">
+      <c r="G35" t="n">
         <v>6131.21580818516</v>
       </c>
-      <c r="H35">
+      <c r="H35" t="n">
         <v>5540.17417054343</v>
       </c>
-      <c r="I35">
+      <c r="I35" t="n">
         <v>6026</v>
       </c>
-      <c r="J35">
+      <c r="J35" t="n">
         <v>6261</v>
       </c>
-      <c r="K35">
+      <c r="K35" t="n">
         <v>6634</v>
       </c>
-      <c r="L35">
+      <c r="L35" t="n">
         <v>6557</v>
       </c>
-      <c r="M35">
+      <c r="M35" t="n">
         <v>7017</v>
       </c>
-      <c r="N35">
+      <c r="N35" t="n">
         <v>8245.15918225426</v>
       </c>
-      <c r="O35">
+      <c r="O35" t="n">
         <v>8777</v>
       </c>
-      <c r="P35">
+      <c r="P35" t="n">
         <v>9081</v>
       </c>
-      <c r="Q35">
+      <c r="Q35" t="n">
         <v>8426</v>
       </c>
-      <c r="R35">
+      <c r="R35" t="n">
         <v>8555</v>
       </c>
-      <c r="S35">
+      <c r="S35" t="n">
         <v>8455</v>
       </c>
-      <c r="T35">
+      <c r="T35" t="n">
         <v>7807</v>
       </c>
-    </row>
-    <row r="36" spans="1:20">
-      <c r="A36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B36">
+      <c r="U35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>长沙</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
         <v>2644.14995024849</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="n">
         <v>3304.74366121187</v>
       </c>
-      <c r="D36">
+      <c r="D36" t="n">
         <v>3288</v>
       </c>
-      <c r="E36">
+      <c r="E36" t="n">
         <v>3648</v>
       </c>
-      <c r="F36">
+      <c r="F36" t="n">
         <v>4418</v>
       </c>
-      <c r="G36">
+      <c r="G36" t="n">
         <v>5862.39008776535</v>
       </c>
-      <c r="H36">
+      <c r="H36" t="n">
         <v>6100.86975200885</v>
       </c>
-      <c r="I36">
+      <c r="I36" t="n">
         <v>6292</v>
       </c>
-      <c r="J36">
+      <c r="J36" t="n">
         <v>6116</v>
       </c>
-      <c r="K36">
+      <c r="K36" t="n">
         <v>5856</v>
       </c>
-      <c r="L36">
+      <c r="L36" t="n">
         <v>6410</v>
       </c>
-      <c r="M36">
+      <c r="M36" t="n">
         <v>7691</v>
       </c>
-      <c r="N36">
+      <c r="N36" t="n">
         <v>8206.492034669431</v>
       </c>
-      <c r="O36">
+      <c r="O36" t="n">
         <v>8657</v>
       </c>
-      <c r="P36">
+      <c r="P36" t="n">
         <v>9238</v>
       </c>
-      <c r="Q36">
+      <c r="Q36" t="n">
         <v>10055</v>
       </c>
-      <c r="R36">
+      <c r="R36" t="n">
         <v>10532</v>
       </c>
-      <c r="S36">
+      <c r="S36" t="n">
         <v>11091</v>
       </c>
-      <c r="T36">
+      <c r="T36" t="n">
         <v>9819</v>
       </c>
-    </row>
-    <row r="37" spans="1:20">
-      <c r="A37" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B37">
+      <c r="U36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>青岛</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
         <v>4249.0603258094</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="n">
         <v>5200.54650809052</v>
       </c>
-      <c r="D37">
+      <c r="D37" t="n">
         <v>5094</v>
       </c>
-      <c r="E37">
+      <c r="E37" t="n">
         <v>5576</v>
       </c>
-      <c r="F37">
+      <c r="F37" t="n">
         <v>6576</v>
       </c>
-      <c r="G37">
+      <c r="G37" t="n">
         <v>7495.44353611309</v>
       </c>
-      <c r="H37">
+      <c r="H37" t="n">
         <v>8056.08723437661</v>
       </c>
-      <c r="I37">
+      <c r="I37" t="n">
         <v>8435</v>
       </c>
-      <c r="J37">
+      <c r="J37" t="n">
         <v>8344</v>
       </c>
-      <c r="K37">
+      <c r="K37" t="n">
         <v>8902</v>
       </c>
-      <c r="L37">
+      <c r="L37" t="n">
         <v>9230</v>
       </c>
-      <c r="M37">
+      <c r="M37" t="n">
         <v>10518</v>
       </c>
-      <c r="N37">
+      <c r="N37" t="n">
         <v>12624.1169192546</v>
       </c>
-      <c r="O37">
+      <c r="O37" t="n">
         <v>13603</v>
       </c>
-      <c r="P37">
+      <c r="P37" t="n">
         <v>13406</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" t="n">
         <v>13787</v>
       </c>
-      <c r="R37">
+      <c r="R37" t="n">
         <v>13946</v>
       </c>
-      <c r="S37">
+      <c r="S37" t="n">
         <v>13926</v>
       </c>
-      <c r="T37">
+      <c r="T37" t="n">
         <v>13765</v>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>